--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_422_Lebanon.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_422_Lebanon.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Racfc26a6f7dd49d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb7d898947559475b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb7c7952af31b40e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb1752fa91c8d47a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R57849a3b0aaf41a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra15940e6aa3e46ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rab44d47dbe6e43d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd41041a6dd7d40f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfacf7a357c514fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rdc15e758eb324e48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R344be853d5b34a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R21c8a22fb3c44afa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ422CommercialTable" displayName="EEZ422CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ422CommercialTable" displayName="EEZ422CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ422FunctionalTable" displayName="EEZ422FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ422FunctionalTable" displayName="EEZ422FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ422ValidationTable" displayName="EEZ422ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ422ValidationTable" displayName="EEZ422ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7863,7 +7817,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R356072e76ecd4146"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recd7bb811d4748f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7873,20 +7827,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7894,606 +7838,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>780.0782265060001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1100090252305095</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82763235506016</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>780.0782265060001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82792992179918</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$108,A2,'Species'!$U$2:$U$108))</x:f>
-        <x:v>100495.86309783637</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1100090252305095</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82763235506016</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>100495.63097250233</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0.2321253340342082</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000023098052302</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0000023098052302166494</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>23.863439248000002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.91</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>812.8305161640995</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>23.863439248000002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$108,A3,'Species'!$U$2:$U$108))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>19396.931641402472</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.91</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>19396.931641402472</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>112.337422097</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.9394531149789342</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>86.98675199251848</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>112.337422097</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>123.087229407457</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$108,A4,'Species'!$U$2:$U$108))</x:f>
-        <x:v>13827.302044695769</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.9394531149789342</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>86.98675199251848</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>9771.867475430605</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4055.434569265164</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.4150112124895</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.41501121248949996</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>67.55346649500001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.216672619386502</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>164.6920439080246</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>67.55346649500001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>174.06604135509863</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$108,A5,'Species'!$U$2:$U$108))</x:f>
-        <x:v>11758.76449259894</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.216672619386502</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>164.6920439080246</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>11125.51847013381</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>633.2460224651313</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0569183381579084</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.05691833815790835</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>939.518664869</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.205509161936918</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>160.51261197040424</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>939.518664869</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>164.75912639992424</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$108,A6,'Species'!$U$2:$U$108))</x:f>
-        <x:v>154794.27446023963</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.205509161936918</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>160.51261197040424</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>150804.59489307005</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3989.6795671695727</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0264559549395593</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.02645595493955941</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>636.7823094419998</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3197234802310014</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>208.79662779023846</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>636.7823094419998</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>225.63216613411873</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$108,A7,'Species'!$U$2:$U$108))</x:f>
-        <x:v>143678.5718352851</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3197234802310014</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>208.79662779023846</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>132957.9988479697</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>10720.57298731542</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0806312751410603</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.08063127514106028</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3411.715303958</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6093742003868075</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>406.79368312827233</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3411.715303958</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>801.2932218924685</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$108,A8,'Species'!$U$2:$U$108))</x:f>
-        <x:v>2733784.3480883483</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6093742003868075</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>406.79368312827233</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1387864.2342821679</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1345920.1138061804</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.9697779368904325</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.9697779368904323</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>106.610617663</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9216180000711116</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>834.8683555410231</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>106.610617663</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>836.6561937773436</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$108,A9,'Species'!$U$2:$U$108))</x:f>
-        <x:v>89196.43359017721</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9216180000711116</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>834.8683555410231</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>89005.83105152156</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>190.60253865565755</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.002141461254885</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0021414612548848193</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>27.152092346</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.063529394133566</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1157.522373441867</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>27.152092346</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1172.1288976965473</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$108,A10,'Species'!$U$2:$U$108))</x:f>
-        <x:v>31825.752071671835</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.063529394133566</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1157.522373441867</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>31429.15437625467</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>396.5976954171638</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0126187835240263</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.01261878352402637</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>381.83521149089995</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.431613221691329</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2701.551317921002</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>381.83521149089995</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2763.8702834084806</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$108,A11,'Species'!$U$2:$U$108))</x:f>
-        <x:v>1055342.9941986909</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.431613221691329</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2701.551317921002</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1031547.4188318853</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>23795.57536680554</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0230678444174204</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.02306784441742041</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12ea0415382c4401"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R235d5556f9894448"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8503,20 +8053,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8524,1092 +8064,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>73.97256824800002</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6305447417498717</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>427.114919273461</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>73.97256824800002</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>431.73090025515467</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$108,A2,'Species'!$U$2:$U$108))</x:f>
-        <x:v>31936.243483894916</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6305447417498717</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>427.114919273461</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>31594.787515695112</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>341.45596819980346</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0108073513085087</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.01080735130850875</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>102.291498013</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.6555882804741735</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>452.46842773731396</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>102.291498013</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>863.3803373604803</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$108,A3,'Species'!$U$2:$U$108))</x:f>
-        <x:v>88316.46806357284</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.6555882804741735</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>452.46842773731396</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>46283.673276836686</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>42032.79478673616</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.9081559826793622</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.9081559826793623</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>55.480215744</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.114510775603591</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1301.6996126163997</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>55.480215744</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1310.2844290013247</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$108,A4,'Species'!$U$2:$U$108))</x:f>
-        <x:v>72694.86280699735</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.114510775603591</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1301.6996126163997</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>72218.57534183908</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>476.2874651582679</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0065950825380285</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.006595082538028629</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>460.90356827489995</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.444935086422188</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2785.704760903641</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>460.90356827489995</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2829.0003564624985</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$108,A5,'Species'!$U$2:$U$108))</x:f>
-        <x:v>1303896.3589445294</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.444935086422188</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2785.704760903641</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1283941.2644608652</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>19955.09448366426</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0155420618029933</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0155420618029934</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>26.526640455</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.0596634712181086</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1147.2642777645697</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>26.526640455</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1159.904150168844</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$108,A6,'Species'!$U$2:$U$108))</x:f>
-        <x:v>30768.36035379125</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.0596634712181086</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1147.2642777645697</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>30433.06700312599</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>335.2933506652589</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0110174025717098</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.011017402571709864</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>310.992470781</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.276892571481576</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1891.8755801632692</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>310.992470781</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2220.018273018649</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$108,A7,'Species'!$U$2:$U$108))</x:f>
-        <x:v>690408.9679050383</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.276892571481576</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1891.8755801632692</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>588359.061085213</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>102049.9068198253</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1734483473945263</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.17344834739452622</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.6254518910000001</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.227490761395748</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1688.4599410494745</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.6254518910000001</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1690.6043983494599</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$108,A8,'Species'!$U$2:$U$108))</x:f>
-        <x:v>1057.391717880587</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.227490761395748</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1688.4599410494745</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1056.0504630071425</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1.3412548734445409</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0012700670284498</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0012700670284498227</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>59.475878916</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.1522471789733246</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>141.98654090393381</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>59.475878916</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>187.9334603676108</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$108,A9,'Species'!$U$2:$U$108))</x:f>
-        <x:v>11177.507733088903</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.1522471789733246</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>141.98654090393381</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>8444.77431450405</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>2732.733418584854</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.3236005270018094</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.3236005270018094</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>58.665648811000004</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3499999999999996</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.87211385683378</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>58.665648811000004</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$108,A10,'Species'!$U$2:$U$108))</x:f>
-        <x:v>13133.60281010123</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3499999999999996</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.87211385683378</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>13133.602810101218</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1.2732925824820995e-11</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>9.694922260804127e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>787.1188705440001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.505426457465729</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>320.2037822218089</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>787.1188705440001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>369.43807821964515</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$108,A11,'Species'!$U$2:$U$108))</x:f>
-        <x:v>290791.68286419305</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.505426457465729</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>320.2037822218089</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>252038.4394063472</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>38753.24345784585</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1537592581081102</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.15375925810811028</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1032.7529225239998</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2630688180769756</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>183.2604792963807</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1032.7529225239998</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>201.94338721962424</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$108,A12,'Species'!$U$2:$U$108))</x:f>
-        <x:v>208557.62333546267</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2630688180769756</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>183.2604792963807</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>189262.79557648613</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>19294.82775897655</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1019472828783141</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.10194728287831402</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>693.780655247</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.135352544513537</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1365.6913054262386</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>693.780655247</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1420.366085416766</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$108,A13,'Species'!$U$2:$U$108))</x:f>
-        <x:v>985422.5134310604</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.135352544513537</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1365.6913054262386</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>947490.2087437466</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>37932.304687313735</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0400345083645848</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.04003450836458482</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>802.831833301</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.212761441184183</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>163.21551555646244</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>802.831833301</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>389.1692261046987</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$108,A14,'Species'!$U$2:$U$108))</x:f>
-        <x:v>312437.4432579666</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.212761441184183</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>163.21551555646244</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>131034.61157736262</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>181402.83168060397</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.3843886702675046</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.3843886702675043</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>52.861543181</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.7000330522532052</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>50.122537824668186</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>52.861543181</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>50.12707068603476</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$108,A15,'Species'!$U$2:$U$108))</x:f>
-        <x:v>2649.794311606866</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.7000330522532052</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>50.122537824668186</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>2649.554697560003</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0.23961404686269816</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.000090435591718</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.00009043559171786894</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>74.77360979</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.439938366447562</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>275.3837860577118</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>74.77360979</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>285.21341981851435</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$108,A16,'Species'!$U$2:$U$108))</x:f>
-        <x:v>21326.436960381045</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.439938366447562</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>275.3837860577118</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>20591.439761172183</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>734.9971992088613</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0356943083015882</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.035694308301588186</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>50.977609459</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.222043423954272</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>166.74139245156877</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>50.977609459</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>167.90229367244302</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$108,A17,'Species'!$U$2:$U$108))</x:f>
-        <x:v>8559.257554104128</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.222043423954272</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>166.74139245156877</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>8500.077585045923</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>59.17996905820473</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0069622857516405</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0069622857516405835</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1764.007171701</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.163139390173845</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>145.59262964081563</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1764.007171701</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>148.71216581068313</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$108,A18,'Species'!$U$2:$U$108))</x:f>
-        <x:v>262329.3270092333</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.163139390173845</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>145.59262964081563</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>256826.44283320635</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>5502.884176026942</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0214264704028189</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.021426470402818847</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>11.855130738999998</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.7552798763841624</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>569.2196401140752</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>11.855130738999998</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>580.2237560159855</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$108,A19,'Species'!$U$2:$U$108))</x:f>
-        <x:v>6878.628485443145</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.7552798763841624</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>569.2196401140752</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>6748.173252758889</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>130.45523268425586</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0193319329243542</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.019331932924354187</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>67.55346649500001</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.216672619386502</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>164.6920439080246</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>67.55346649500001</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>174.06604135509863</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$108,A20,'Species'!$U$2:$U$108))</x:f>
-        <x:v>11758.76449259894</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.216672619386502</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>164.6920439080246</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>11125.51847013381</x:v>
       </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>633.2460224651313</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0569183381579084</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.05691833815790835</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcca29c7a125d452a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4641f5031104e69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9784,7 +8615,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9883,7 +8714,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>4354101.235520946</x:v>
+        <x:v>2964399.180842338</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9897,7 +8728,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>4354101.235520945</x:v>
+        <x:v>3901732.118175007</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9911,7 +8742,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>9.313225746154785e-10</x:v>
+        <x:v>-1389702.0546786068</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9925,7 +8756,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-452369.117345938</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9936,9 +8767,9 @@
         <x:v>EEZ_422</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9950,47 +8781,19 @@
         <x:v>EEZ_422</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_422</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_422</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc25beab6dce458c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc145ef5987bd42a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10037,7 +8840,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
